--- a/output/laminas_comunales/comunal_s_isapre_a_2024_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2024_metropolitana.xlsx
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C2">
-        <v>200135</v>
+        <v>78.69025105597518</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C3">
-        <v>115591</v>
+        <v>65.92756812312233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C4">
-        <v>94881</v>
+        <v>62.35314964118012</v>
       </c>
     </row>
     <row r="5">
@@ -429,367 +429,367 @@
         </is>
       </c>
       <c r="C5">
-        <v>93911</v>
+        <v>58.87357143304934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="C6">
-        <v>87953</v>
+        <v>49.27275275750159</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="C7">
-        <v>77397</v>
+        <v>48.60726810929918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="C8">
-        <v>72089</v>
+        <v>31.86092529158223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="C9">
-        <v>70378</v>
+        <v>30.78656579333592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="C10">
-        <v>69489</v>
+        <v>29.34850023513696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="C11">
-        <v>53296</v>
+        <v>23.06421412049785</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="C12">
-        <v>49000</v>
+        <v>22.83603828547649</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="C13">
-        <v>45699</v>
+        <v>20.64999306304095</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="C14">
-        <v>43061</v>
+        <v>20.44213415880618</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C15">
-        <v>32514</v>
+        <v>20.41663438944406</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="C16">
-        <v>31803</v>
+        <v>18.77640162073623</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="C17">
-        <v>30638</v>
+        <v>18.13841546590571</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="C18">
-        <v>29316</v>
+        <v>17.92004205310427</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="C19">
-        <v>28908</v>
+        <v>17.82492526652734</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="C20">
-        <v>23137</v>
+        <v>16.27987816990002</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="C21">
-        <v>19670</v>
+        <v>16.2167304902124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="C22">
-        <v>17277</v>
+        <v>14.94446118113527</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="C23">
-        <v>15757</v>
+        <v>14.90418636911094</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="C24">
-        <v>15378</v>
+        <v>13.75642526337218</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="C25">
-        <v>13636</v>
+        <v>13.37996890961581</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="C26">
-        <v>13386</v>
+        <v>13.32152303009132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="C27">
-        <v>12255</v>
+        <v>13.01060363295948</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="C28">
-        <v>12215</v>
+        <v>12.97003303275208</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="C29">
-        <v>10847</v>
+        <v>12.80149585818596</v>
       </c>
     </row>
     <row r="30">
@@ -804,352 +804,352 @@
         </is>
       </c>
       <c r="C30">
-        <v>10842</v>
+        <v>12.62841568243763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="C31">
-        <v>10678</v>
+        <v>11.35054068987292</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="C32">
-        <v>10236</v>
+        <v>11.07000501229205</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="C33">
-        <v>10169</v>
+        <v>10.11867866051856</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="C34">
-        <v>9989</v>
+        <v>10.02270303514064</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="C35">
-        <v>9810</v>
+        <v>10.00081039153488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="C36">
-        <v>7599</v>
+        <v>9.997953754859832</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="C37">
-        <v>7480</v>
+        <v>9.793705216118346</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="C38">
-        <v>6852</v>
+        <v>9.36367201892107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="C39">
-        <v>6738</v>
+        <v>9.115336172254544</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="C40">
-        <v>6567</v>
+        <v>8.13853639919855</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="C41">
-        <v>6534</v>
+        <v>7.475512288924945</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="C42">
-        <v>5990</v>
+        <v>7.339815811020212</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="C43">
-        <v>4638</v>
+        <v>7.195559531711447</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="C44">
-        <v>4537</v>
+        <v>6.906016233182616</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="C45">
-        <v>4314</v>
+        <v>6.902532084634061</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="C46">
-        <v>4038</v>
+        <v>6.395032408094602</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="C47">
-        <v>3920</v>
+        <v>6.15440595239589</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="C48">
-        <v>2703</v>
+        <v>5.583942498105274</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="C49">
-        <v>2585</v>
+        <v>4.695458033907765</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="C50">
-        <v>2195</v>
+        <v>4.368085990767952</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="C51">
-        <v>1244</v>
+        <v>4.276259969455286</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="C52">
-        <v>1205</v>
+        <v>3.911121753619284</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>La Pintana</t>
         </is>
       </c>
       <c r="C53">
-        <v>504</v>
+        <v>2.530000892219843</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
